--- a/docs/shows/data/shows.xlsx
+++ b/docs/shows/data/shows.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings_website/rock/docs/shows/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings_website/rock/docs/shows/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64CFBEF2-8A23-C74A-9FF3-612B706D2BE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C7D9926-12B6-6E4F-A1E4-FBE4F7F6376A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="166">
   <si>
     <t>HOW TO ADD A SHOW: Fill in a new row below. Date format: YYYY-MM-DD. Start/End Time: H:MM AM/PM (e.g. 7:00 PM). Address: full street address for Maps link (e.g. 1600 Dodge Ave, Evanston, IL 60201). Cancelled: TRUE or FALSE. Cancel Reason: optional text like "venue closure" (defaults to weather). Private: TRUE for private bookings (hidden from calendar/search). Leave optional columns blank if not needed. After saving, run:  python docs/shows/update_shows.py  then commit &amp; push.</t>
   </si>
@@ -563,6 +563,9 @@
   </si>
   <si>
     <t>https://www.instagram.com/p/DZ2hJvMDgf9/?utm_source=ig_web_copy_link&amp;igsh=MzRlODBiNWFlZA==</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/p/DQkITMGAcL4/</t>
   </si>
 </sst>
 </file>
@@ -1513,6 +1516,9 @@
       </c>
       <c r="H17" s="8"/>
       <c r="I17" s="14"/>
+      <c r="P17" s="11" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="18" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">

--- a/docs/shows/data/shows.xlsx
+++ b/docs/shows/data/shows.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings_website/rock/docs/shows/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C7D9926-12B6-6E4F-A1E4-FBE4F7F6376A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A97A4A60-B35F-6946-89C9-4A2D7B91AD83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,8 +34,90 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Miles Shultz</author>
+  </authors>
+  <commentList>
+    <comment ref="U2" authorId="0" shapeId="0" xr:uid="{2E4392CE-DD70-D64B-A183-5B88784BBF8D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Miles Shultz:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Weather source: Open-Meteo historical daily data for Evanston (42.07N, 87.77W). Columns Q-U populated from uploaded open-meteo CSV.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q25" authorId="0" shapeId="0" xr:uid="{686F06D2-8E57-3B40-B498-3EBE086777BF}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Miles Shultz:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+No weather data: 2026-09-12 is beyond the uploaded Open-Meteo dataset (ends 2026-06-24).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q26" authorId="0" shapeId="0" xr:uid="{917A5EBA-09F0-3647-8A8E-49DEDD34940E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Miles Shultz:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+No weather data: 2027-09-11 is beyond the uploaded Open-Meteo dataset (ends 2026-06-24).</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="171">
   <si>
     <t>HOW TO ADD A SHOW: Fill in a new row below. Date format: YYYY-MM-DD. Start/End Time: H:MM AM/PM (e.g. 7:00 PM). Address: full street address for Maps link (e.g. 1600 Dodge Ave, Evanston, IL 60201). Cancelled: TRUE or FALSE. Cancel Reason: optional text like "venue closure" (defaults to weather). Private: TRUE for private bookings (hidden from calendar/search). Leave optional columns blank if not needed. After saving, run:  python docs/shows/update_shows.py  then commit &amp; push.</t>
   </si>
@@ -567,12 +649,36 @@
   <si>
     <t>https://www.instagram.com/p/DQkITMGAcL4/</t>
   </si>
+  <si>
+    <t>Temp High
+(°F)</t>
+  </si>
+  <si>
+    <t>Temp Low
+(°F)</t>
+  </si>
+  <si>
+    <t>Precipitation
+(inch)</t>
+  </si>
+  <si>
+    <t>Cloud Cover
+(%)</t>
+  </si>
+  <si>
+    <t>Wind Max
+(mph)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+  </numFmts>
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -645,6 +751,26 @@
       <color rgb="FF1F1F1F"/>
       <name val="Courier New"/>
       <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Courier New"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="8">
@@ -733,7 +859,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -791,6 +917,18 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -806,6 +944,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1091,9 +1233,31 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{3E5FF9E1-556A-CD49-97B7-C88C5B7FE7D1}">
+  <we:reference id="wa200009404" version="1.0.0.8" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;66ed22f7-61b9-4d59-a90f-0b234e594dde&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P31"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:U31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" style="11" customWidth="1"/>
@@ -1110,10 +1274,12 @@
     <col min="12" max="12" width="118.83203125" style="11" bestFit="1" customWidth="1"/>
     <col min="13" max="14" width="8.83203125" style="11" customWidth="1"/>
     <col min="15" max="15" width="8.83203125" customWidth="1"/>
-    <col min="16" max="16384" width="8.83203125" style="11"/>
+    <col min="16" max="16" width="8.83203125" style="11"/>
+    <col min="17" max="21" width="12.5" style="11" customWidth="1"/>
+    <col min="22" max="16384" width="8.83203125" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -1126,7 +1292,7 @@
       <c r="H1" s="17"/>
       <c r="I1" s="17"/>
     </row>
-    <row r="2" spans="1:16" ht="54" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" ht="54" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>1</v>
       </c>
@@ -1175,8 +1341,23 @@
       <c r="P2" s="11" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q2" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="R2" s="21" t="s">
+        <v>167</v>
+      </c>
+      <c r="S2" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="T2" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="U2" s="21" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>16</v>
       </c>
@@ -1198,8 +1379,23 @@
       <c r="L3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q3" s="22">
+        <v>69.3</v>
+      </c>
+      <c r="R3" s="22">
+        <v>59</v>
+      </c>
+      <c r="S3" s="23">
+        <v>0</v>
+      </c>
+      <c r="T3" s="24">
+        <v>21</v>
+      </c>
+      <c r="U3" s="22">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>20</v>
       </c>
@@ -1221,8 +1417,23 @@
         <v>23</v>
       </c>
       <c r="I4" s="14"/>
-    </row>
-    <row r="5" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q4" s="22">
+        <v>58.4</v>
+      </c>
+      <c r="R4" s="22">
+        <v>41.6</v>
+      </c>
+      <c r="S4" s="23">
+        <v>8.3000000000000004E-2</v>
+      </c>
+      <c r="T4" s="24">
+        <v>97</v>
+      </c>
+      <c r="U4" s="22">
+        <v>17.600000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>24</v>
       </c>
@@ -1243,8 +1454,23 @@
       <c r="P5" s="11" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q5" s="22">
+        <v>75.3</v>
+      </c>
+      <c r="R5" s="22">
+        <v>58.7</v>
+      </c>
+      <c r="S5" s="23">
+        <v>0</v>
+      </c>
+      <c r="T5" s="24">
+        <v>31</v>
+      </c>
+      <c r="U5" s="22">
+        <v>17.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>28</v>
       </c>
@@ -1265,8 +1491,23 @@
       <c r="P6" s="11" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q6" s="22">
+        <v>79</v>
+      </c>
+      <c r="R6" s="22">
+        <v>63.6</v>
+      </c>
+      <c r="S6" s="23">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="T6" s="24">
+        <v>60</v>
+      </c>
+      <c r="U6" s="22">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>32</v>
       </c>
@@ -1279,8 +1520,23 @@
       <c r="F7" s="8"/>
       <c r="H7" s="8"/>
       <c r="I7" s="14"/>
-    </row>
-    <row r="8" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q7" s="22">
+        <v>79.8</v>
+      </c>
+      <c r="R7" s="22">
+        <v>68</v>
+      </c>
+      <c r="S7" s="23">
+        <v>0.47599999999999998</v>
+      </c>
+      <c r="T7" s="24">
+        <v>49</v>
+      </c>
+      <c r="U7" s="22">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
         <v>34</v>
       </c>
@@ -1301,8 +1557,23 @@
       <c r="P8" s="11" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q8" s="22">
+        <v>82.9</v>
+      </c>
+      <c r="R8" s="22">
+        <v>60.8</v>
+      </c>
+      <c r="S8" s="23">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="T8" s="24">
+        <v>23</v>
+      </c>
+      <c r="U8" s="22">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>35</v>
       </c>
@@ -1324,8 +1595,23 @@
       <c r="L9" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q9" s="22">
+        <v>60.6</v>
+      </c>
+      <c r="R9" s="22">
+        <v>50.6</v>
+      </c>
+      <c r="S9" s="23">
+        <v>1.2E-2</v>
+      </c>
+      <c r="T9" s="24">
+        <v>2</v>
+      </c>
+      <c r="U9" s="22">
+        <v>14.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>36</v>
       </c>
@@ -1354,8 +1640,23 @@
       <c r="P10" s="11" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q10" s="22">
+        <v>65.7</v>
+      </c>
+      <c r="R10" s="22">
+        <v>48.7</v>
+      </c>
+      <c r="S10" s="23">
+        <v>0</v>
+      </c>
+      <c r="T10" s="24">
+        <v>5</v>
+      </c>
+      <c r="U10" s="22">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>40</v>
       </c>
@@ -1380,8 +1681,23 @@
       <c r="P11" s="11" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="12" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q11" s="22">
+        <v>57.8</v>
+      </c>
+      <c r="R11" s="22">
+        <v>41.8</v>
+      </c>
+      <c r="S11" s="23">
+        <v>0</v>
+      </c>
+      <c r="T11" s="24">
+        <v>70</v>
+      </c>
+      <c r="U11" s="22">
+        <v>16.100000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>41</v>
       </c>
@@ -1402,8 +1718,23 @@
       <c r="P12" s="11" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q12" s="22">
+        <v>69.099999999999994</v>
+      </c>
+      <c r="R12" s="22">
+        <v>54</v>
+      </c>
+      <c r="S12" s="23">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="T12" s="24">
+        <v>72</v>
+      </c>
+      <c r="U12" s="22">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
         <v>42</v>
       </c>
@@ -1424,8 +1755,23 @@
       <c r="P13" s="11" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q13" s="22">
+        <v>75.7</v>
+      </c>
+      <c r="R13" s="22">
+        <v>67.7</v>
+      </c>
+      <c r="S13" s="23">
+        <v>0.23200000000000001</v>
+      </c>
+      <c r="T13" s="24">
+        <v>80</v>
+      </c>
+      <c r="U13" s="22">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
         <v>46</v>
       </c>
@@ -1444,8 +1790,23 @@
       <c r="L14" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q14" s="22">
+        <v>64.8</v>
+      </c>
+      <c r="R14" s="22">
+        <v>50.2</v>
+      </c>
+      <c r="S14" s="23">
+        <v>0</v>
+      </c>
+      <c r="T14" s="24">
+        <v>35</v>
+      </c>
+      <c r="U14" s="22">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>47</v>
       </c>
@@ -1466,8 +1827,23 @@
       <c r="J15" s="11" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q15" s="22">
+        <v>65.5</v>
+      </c>
+      <c r="R15" s="22">
+        <v>48</v>
+      </c>
+      <c r="S15" s="23">
+        <v>8.3000000000000004E-2</v>
+      </c>
+      <c r="T15" s="24">
+        <v>54</v>
+      </c>
+      <c r="U15" s="22">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
         <v>52</v>
       </c>
@@ -1493,8 +1869,23 @@
       <c r="P16" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="17" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q16" s="22">
+        <v>74.099999999999994</v>
+      </c>
+      <c r="R16" s="22">
+        <v>59.6</v>
+      </c>
+      <c r="S16" s="23">
+        <v>0.27600000000000002</v>
+      </c>
+      <c r="T16" s="24">
+        <v>91</v>
+      </c>
+      <c r="U16" s="22">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
         <v>58</v>
       </c>
@@ -1519,8 +1910,23 @@
       <c r="P17" s="11" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="18" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q17" s="22">
+        <v>50.6</v>
+      </c>
+      <c r="R17" s="22">
+        <v>37.1</v>
+      </c>
+      <c r="S17" s="23">
+        <v>0</v>
+      </c>
+      <c r="T17" s="24">
+        <v>0</v>
+      </c>
+      <c r="U17" s="22">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
         <v>62</v>
       </c>
@@ -1545,8 +1951,23 @@
       <c r="P18" s="11" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="19" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q18" s="22">
+        <v>5</v>
+      </c>
+      <c r="R18" s="22">
+        <v>-10.3</v>
+      </c>
+      <c r="S18" s="23">
+        <v>3.1E-2</v>
+      </c>
+      <c r="T18" s="24">
+        <v>100</v>
+      </c>
+      <c r="U18" s="22">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
         <v>66</v>
       </c>
@@ -1573,8 +1994,23 @@
       <c r="P19" s="11" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="20" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q19" s="22">
+        <v>69.099999999999994</v>
+      </c>
+      <c r="R19" s="22">
+        <v>48.6</v>
+      </c>
+      <c r="S19" s="23">
+        <v>5.5E-2</v>
+      </c>
+      <c r="T19" s="24">
+        <v>97</v>
+      </c>
+      <c r="U19" s="22">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
         <v>160</v>
       </c>
@@ -1599,8 +2035,23 @@
       <c r="P20" s="11" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="21" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q20" s="22">
+        <v>52.4</v>
+      </c>
+      <c r="R20" s="22">
+        <v>34.299999999999997</v>
+      </c>
+      <c r="S20" s="23">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="T20" s="24">
+        <v>42</v>
+      </c>
+      <c r="U20" s="22">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
         <v>68</v>
       </c>
@@ -1633,8 +2084,23 @@
       <c r="P21" s="11" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="22" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q21" s="22">
+        <v>63.2</v>
+      </c>
+      <c r="R21" s="22">
+        <v>42.2</v>
+      </c>
+      <c r="S21" s="23">
+        <v>0</v>
+      </c>
+      <c r="T21" s="24">
+        <v>21</v>
+      </c>
+      <c r="U21" s="22">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
         <v>70</v>
       </c>
@@ -1650,8 +2116,23 @@
       <c r="G22" s="8"/>
       <c r="H22" s="8"/>
       <c r="I22" s="14"/>
-    </row>
-    <row r="23" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q22" s="22">
+        <v>84.8</v>
+      </c>
+      <c r="R22" s="22">
+        <v>60.9</v>
+      </c>
+      <c r="S22" s="23">
+        <v>0.25600000000000001</v>
+      </c>
+      <c r="T22" s="24">
+        <v>84</v>
+      </c>
+      <c r="U22" s="22">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
         <v>72</v>
       </c>
@@ -1684,8 +2165,23 @@
       <c r="P23" s="11" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="24" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q23" s="22">
+        <v>71.8</v>
+      </c>
+      <c r="R23" s="22">
+        <v>60.6</v>
+      </c>
+      <c r="S23" s="23">
+        <v>0.82699999999999996</v>
+      </c>
+      <c r="T23" s="24">
+        <v>100</v>
+      </c>
+      <c r="U23" s="22">
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
         <v>77</v>
       </c>
@@ -1716,8 +2212,23 @@
       <c r="P24" s="11" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="25" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q24" s="22">
+        <v>70.3</v>
+      </c>
+      <c r="R24" s="22">
+        <v>58.8</v>
+      </c>
+      <c r="S24" s="23">
+        <v>0.95699999999999996</v>
+      </c>
+      <c r="T24" s="24">
+        <v>51</v>
+      </c>
+      <c r="U24" s="22">
+        <v>8.3000000000000007</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
         <v>83</v>
       </c>
@@ -1740,7 +2251,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
         <v>85</v>
       </c>
@@ -1763,7 +2274,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="L31" s="11" t="s">
         <v>159</v>
       </c>
@@ -1773,6 +2284,7 @@
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/docs/shows/data/shows.xlsx
+++ b/docs/shows/data/shows.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings_website/rock/docs/shows/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A97A4A60-B35F-6946-89C9-4A2D7B91AD83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6CD7570-48AD-B142-9CC7-9B5DF152F9B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -388,9 +388,6 @@
     <t>4:00 PM</t>
   </si>
   <si>
-    <t>2027-09-11</t>
-  </si>
-  <si>
     <t>How To Add a New Show</t>
   </si>
   <si>
@@ -668,6 +665,9 @@
   <si>
     <t>Wind Max
 (mph)</t>
+  </si>
+  <si>
+    <t>2027-09-11</t>
   </si>
 </sst>
 </file>
@@ -904,6 +904,18 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -916,18 +928,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -944,10 +944,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1280,17 +1276,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
     </row>
     <row r="2" spans="1:21" ht="54" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
@@ -1339,22 +1335,22 @@
         <v>15</v>
       </c>
       <c r="P2" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="Q2" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q2" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="R2" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="R2" s="21" t="s">
+      <c r="S2" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="S2" s="21" t="s">
+      <c r="T2" s="16" t="s">
         <v>168</v>
       </c>
-      <c r="T2" s="21" t="s">
+      <c r="U2" s="16" t="s">
         <v>169</v>
-      </c>
-      <c r="U2" s="21" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -1379,19 +1375,19 @@
       <c r="L3" t="s">
         <v>19</v>
       </c>
-      <c r="Q3" s="22">
+      <c r="Q3" s="17">
         <v>69.3</v>
       </c>
-      <c r="R3" s="22">
+      <c r="R3" s="17">
         <v>59</v>
       </c>
-      <c r="S3" s="23">
+      <c r="S3" s="18">
         <v>0</v>
       </c>
-      <c r="T3" s="24">
+      <c r="T3" s="19">
         <v>21</v>
       </c>
-      <c r="U3" s="22">
+      <c r="U3" s="17">
         <v>9.6</v>
       </c>
     </row>
@@ -1417,19 +1413,19 @@
         <v>23</v>
       </c>
       <c r="I4" s="14"/>
-      <c r="Q4" s="22">
+      <c r="Q4" s="17">
         <v>58.4</v>
       </c>
-      <c r="R4" s="22">
+      <c r="R4" s="17">
         <v>41.6</v>
       </c>
-      <c r="S4" s="23">
+      <c r="S4" s="18">
         <v>8.3000000000000004E-2</v>
       </c>
-      <c r="T4" s="24">
+      <c r="T4" s="19">
         <v>97</v>
       </c>
-      <c r="U4" s="22">
+      <c r="U4" s="17">
         <v>17.600000000000001</v>
       </c>
     </row>
@@ -1452,21 +1448,21 @@
       <c r="H5" s="8"/>
       <c r="I5" s="14"/>
       <c r="P5" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="Q5" s="22">
+        <v>149</v>
+      </c>
+      <c r="Q5" s="17">
         <v>75.3</v>
       </c>
-      <c r="R5" s="22">
+      <c r="R5" s="17">
         <v>58.7</v>
       </c>
-      <c r="S5" s="23">
+      <c r="S5" s="18">
         <v>0</v>
       </c>
-      <c r="T5" s="24">
+      <c r="T5" s="19">
         <v>31</v>
       </c>
-      <c r="U5" s="22">
+      <c r="U5" s="17">
         <v>17.2</v>
       </c>
     </row>
@@ -1489,21 +1485,21 @@
       <c r="H6" s="8"/>
       <c r="I6" s="14"/>
       <c r="P6" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="Q6" s="22">
+        <v>150</v>
+      </c>
+      <c r="Q6" s="17">
         <v>79</v>
       </c>
-      <c r="R6" s="22">
+      <c r="R6" s="17">
         <v>63.6</v>
       </c>
-      <c r="S6" s="23">
+      <c r="S6" s="18">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="T6" s="24">
+      <c r="T6" s="19">
         <v>60</v>
       </c>
-      <c r="U6" s="22">
+      <c r="U6" s="17">
         <v>8</v>
       </c>
     </row>
@@ -1520,19 +1516,19 @@
       <c r="F7" s="8"/>
       <c r="H7" s="8"/>
       <c r="I7" s="14"/>
-      <c r="Q7" s="22">
+      <c r="Q7" s="17">
         <v>79.8</v>
       </c>
-      <c r="R7" s="22">
+      <c r="R7" s="17">
         <v>68</v>
       </c>
-      <c r="S7" s="23">
+      <c r="S7" s="18">
         <v>0.47599999999999998</v>
       </c>
-      <c r="T7" s="24">
+      <c r="T7" s="19">
         <v>49</v>
       </c>
-      <c r="U7" s="22">
+      <c r="U7" s="17">
         <v>9.9</v>
       </c>
     </row>
@@ -1555,21 +1551,21 @@
       <c r="H8" s="8"/>
       <c r="I8" s="14"/>
       <c r="P8" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="Q8" s="22">
+        <v>151</v>
+      </c>
+      <c r="Q8" s="17">
         <v>82.9</v>
       </c>
-      <c r="R8" s="22">
+      <c r="R8" s="17">
         <v>60.8</v>
       </c>
-      <c r="S8" s="23">
+      <c r="S8" s="18">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="T8" s="24">
+      <c r="T8" s="19">
         <v>23</v>
       </c>
-      <c r="U8" s="22">
+      <c r="U8" s="17">
         <v>10.4</v>
       </c>
     </row>
@@ -1595,19 +1591,19 @@
       <c r="L9" t="s">
         <v>19</v>
       </c>
-      <c r="Q9" s="22">
+      <c r="Q9" s="17">
         <v>60.6</v>
       </c>
-      <c r="R9" s="22">
+      <c r="R9" s="17">
         <v>50.6</v>
       </c>
-      <c r="S9" s="23">
+      <c r="S9" s="18">
         <v>1.2E-2</v>
       </c>
-      <c r="T9" s="24">
+      <c r="T9" s="19">
         <v>2</v>
       </c>
-      <c r="U9" s="22">
+      <c r="U9" s="17">
         <v>14.6</v>
       </c>
     </row>
@@ -1638,21 +1634,21 @@
         <v>39</v>
       </c>
       <c r="P10" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="Q10" s="22">
+        <v>152</v>
+      </c>
+      <c r="Q10" s="17">
         <v>65.7</v>
       </c>
-      <c r="R10" s="22">
+      <c r="R10" s="17">
         <v>48.7</v>
       </c>
-      <c r="S10" s="23">
+      <c r="S10" s="18">
         <v>0</v>
       </c>
-      <c r="T10" s="24">
+      <c r="T10" s="19">
         <v>5</v>
       </c>
-      <c r="U10" s="22">
+      <c r="U10" s="17">
         <v>9.1</v>
       </c>
     </row>
@@ -1679,21 +1675,21 @@
       </c>
       <c r="I11" s="14"/>
       <c r="P11" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="Q11" s="22">
+        <v>153</v>
+      </c>
+      <c r="Q11" s="17">
         <v>57.8</v>
       </c>
-      <c r="R11" s="22">
+      <c r="R11" s="17">
         <v>41.8</v>
       </c>
-      <c r="S11" s="23">
+      <c r="S11" s="18">
         <v>0</v>
       </c>
-      <c r="T11" s="24">
+      <c r="T11" s="19">
         <v>70</v>
       </c>
-      <c r="U11" s="22">
+      <c r="U11" s="17">
         <v>16.100000000000001</v>
       </c>
     </row>
@@ -1716,21 +1712,21 @@
       <c r="H12" s="8"/>
       <c r="I12" s="14"/>
       <c r="P12" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q12" s="22">
+        <v>154</v>
+      </c>
+      <c r="Q12" s="17">
         <v>69.099999999999994</v>
       </c>
-      <c r="R12" s="22">
+      <c r="R12" s="17">
         <v>54</v>
       </c>
-      <c r="S12" s="23">
+      <c r="S12" s="18">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="T12" s="24">
+      <c r="T12" s="19">
         <v>72</v>
       </c>
-      <c r="U12" s="22">
+      <c r="U12" s="17">
         <v>7.7</v>
       </c>
     </row>
@@ -1753,21 +1749,21 @@
       <c r="H13" s="8"/>
       <c r="I13" s="14"/>
       <c r="P13" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q13" s="22">
+        <v>155</v>
+      </c>
+      <c r="Q13" s="17">
         <v>75.7</v>
       </c>
-      <c r="R13" s="22">
+      <c r="R13" s="17">
         <v>67.7</v>
       </c>
-      <c r="S13" s="23">
+      <c r="S13" s="18">
         <v>0.23200000000000001</v>
       </c>
-      <c r="T13" s="24">
+      <c r="T13" s="19">
         <v>80</v>
       </c>
-      <c r="U13" s="22">
+      <c r="U13" s="17">
         <v>8</v>
       </c>
     </row>
@@ -1790,19 +1786,19 @@
       <c r="L14" t="s">
         <v>19</v>
       </c>
-      <c r="Q14" s="22">
+      <c r="Q14" s="17">
         <v>64.8</v>
       </c>
-      <c r="R14" s="22">
+      <c r="R14" s="17">
         <v>50.2</v>
       </c>
-      <c r="S14" s="23">
+      <c r="S14" s="18">
         <v>0</v>
       </c>
-      <c r="T14" s="24">
+      <c r="T14" s="19">
         <v>35</v>
       </c>
-      <c r="U14" s="22">
+      <c r="U14" s="17">
         <v>12.6</v>
       </c>
     </row>
@@ -1827,19 +1823,19 @@
       <c r="J15" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="Q15" s="22">
+      <c r="Q15" s="17">
         <v>65.5</v>
       </c>
-      <c r="R15" s="22">
+      <c r="R15" s="17">
         <v>48</v>
       </c>
-      <c r="S15" s="23">
+      <c r="S15" s="18">
         <v>8.3000000000000004E-2</v>
       </c>
-      <c r="T15" s="24">
+      <c r="T15" s="19">
         <v>54</v>
       </c>
-      <c r="U15" s="22">
+      <c r="U15" s="17">
         <v>9.6</v>
       </c>
     </row>
@@ -1867,21 +1863,21 @@
         <v>57</v>
       </c>
       <c r="P16" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q16" s="22">
+        <v>148</v>
+      </c>
+      <c r="Q16" s="17">
         <v>74.099999999999994</v>
       </c>
-      <c r="R16" s="22">
+      <c r="R16" s="17">
         <v>59.6</v>
       </c>
-      <c r="S16" s="23">
+      <c r="S16" s="18">
         <v>0.27600000000000002</v>
       </c>
-      <c r="T16" s="24">
+      <c r="T16" s="19">
         <v>91</v>
       </c>
-      <c r="U16" s="22">
+      <c r="U16" s="17">
         <v>12.3</v>
       </c>
     </row>
@@ -1908,21 +1904,21 @@
       <c r="H17" s="8"/>
       <c r="I17" s="14"/>
       <c r="P17" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="Q17" s="22">
+        <v>164</v>
+      </c>
+      <c r="Q17" s="17">
         <v>50.6</v>
       </c>
-      <c r="R17" s="22">
+      <c r="R17" s="17">
         <v>37.1</v>
       </c>
-      <c r="S17" s="23">
+      <c r="S17" s="18">
         <v>0</v>
       </c>
-      <c r="T17" s="24">
+      <c r="T17" s="19">
         <v>0</v>
       </c>
-      <c r="U17" s="22">
+      <c r="U17" s="17">
         <v>14.2</v>
       </c>
     </row>
@@ -1949,21 +1945,21 @@
       <c r="H18" s="8"/>
       <c r="I18" s="14"/>
       <c r="P18" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="Q18" s="22">
+        <v>156</v>
+      </c>
+      <c r="Q18" s="17">
         <v>5</v>
       </c>
-      <c r="R18" s="22">
+      <c r="R18" s="17">
         <v>-10.3</v>
       </c>
-      <c r="S18" s="23">
+      <c r="S18" s="18">
         <v>3.1E-2</v>
       </c>
-      <c r="T18" s="24">
+      <c r="T18" s="19">
         <v>100</v>
       </c>
-      <c r="U18" s="22">
+      <c r="U18" s="17">
         <v>8.4</v>
       </c>
     </row>
@@ -1992,27 +1988,27 @@
       </c>
       <c r="I19" s="14"/>
       <c r="P19" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="Q19" s="22">
+        <v>157</v>
+      </c>
+      <c r="Q19" s="17">
         <v>69.099999999999994</v>
       </c>
-      <c r="R19" s="22">
+      <c r="R19" s="17">
         <v>48.6</v>
       </c>
-      <c r="S19" s="23">
+      <c r="S19" s="18">
         <v>5.5E-2</v>
       </c>
-      <c r="T19" s="24">
+      <c r="T19" s="19">
         <v>97</v>
       </c>
-      <c r="U19" s="22">
+      <c r="U19" s="17">
         <v>12.4</v>
       </c>
     </row>
     <row r="20" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>21</v>
@@ -2033,21 +2029,21 @@
       </c>
       <c r="I20" s="14"/>
       <c r="P20" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="Q20" s="22">
+        <v>160</v>
+      </c>
+      <c r="Q20" s="17">
         <v>52.4</v>
       </c>
-      <c r="R20" s="22">
+      <c r="R20" s="17">
         <v>34.299999999999997</v>
       </c>
-      <c r="S20" s="23">
+      <c r="S20" s="18">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="T20" s="24">
+      <c r="T20" s="19">
         <v>42</v>
       </c>
-      <c r="U20" s="22">
+      <c r="U20" s="17">
         <v>8.1</v>
       </c>
     </row>
@@ -2082,21 +2078,21 @@
         <v>39</v>
       </c>
       <c r="P21" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="Q21" s="22">
+        <v>161</v>
+      </c>
+      <c r="Q21" s="17">
         <v>63.2</v>
       </c>
-      <c r="R21" s="22">
+      <c r="R21" s="17">
         <v>42.2</v>
       </c>
-      <c r="S21" s="23">
+      <c r="S21" s="18">
         <v>0</v>
       </c>
-      <c r="T21" s="24">
+      <c r="T21" s="19">
         <v>21</v>
       </c>
-      <c r="U21" s="22">
+      <c r="U21" s="17">
         <v>8.4</v>
       </c>
     </row>
@@ -2116,19 +2112,19 @@
       <c r="G22" s="8"/>
       <c r="H22" s="8"/>
       <c r="I22" s="14"/>
-      <c r="Q22" s="22">
+      <c r="Q22" s="17">
         <v>84.8</v>
       </c>
-      <c r="R22" s="22">
+      <c r="R22" s="17">
         <v>60.9</v>
       </c>
-      <c r="S22" s="23">
+      <c r="S22" s="18">
         <v>0.25600000000000001</v>
       </c>
-      <c r="T22" s="24">
+      <c r="T22" s="19">
         <v>84</v>
       </c>
-      <c r="U22" s="22">
+      <c r="U22" s="17">
         <v>10.7</v>
       </c>
     </row>
@@ -2163,21 +2159,21 @@
         <v>1</v>
       </c>
       <c r="P23" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q23" s="22">
+        <v>162</v>
+      </c>
+      <c r="Q23" s="17">
         <v>71.8</v>
       </c>
-      <c r="R23" s="22">
+      <c r="R23" s="17">
         <v>60.6</v>
       </c>
-      <c r="S23" s="23">
+      <c r="S23" s="18">
         <v>0.82699999999999996</v>
       </c>
-      <c r="T23" s="24">
+      <c r="T23" s="19">
         <v>100</v>
       </c>
-      <c r="U23" s="22">
+      <c r="U23" s="17">
         <v>11.6</v>
       </c>
     </row>
@@ -2210,21 +2206,21 @@
         <v>1</v>
       </c>
       <c r="P24" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="Q24" s="22">
+        <v>163</v>
+      </c>
+      <c r="Q24" s="17">
         <v>70.3</v>
       </c>
-      <c r="R24" s="22">
+      <c r="R24" s="17">
         <v>58.8</v>
       </c>
-      <c r="S24" s="23">
+      <c r="S24" s="18">
         <v>0.95699999999999996</v>
       </c>
-      <c r="T24" s="24">
+      <c r="T24" s="19">
         <v>51</v>
       </c>
-      <c r="U24" s="22">
+      <c r="U24" s="17">
         <v>8.3000000000000007</v>
       </c>
     </row>
@@ -2253,7 +2249,7 @@
     </row>
     <row r="26" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
-        <v>85</v>
+        <v>170</v>
       </c>
       <c r="B26" s="8" t="s">
         <v>17</v>
@@ -2276,7 +2272,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="L31" s="11" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -2298,16 +2294,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1" s="23"/>
+    </row>
+    <row r="2" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="B1" s="19"/>
-    </row>
-    <row r="2" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="B2" s="19"/>
+      <c r="B2" s="23"/>
     </row>
     <row r="3" spans="1:2" ht="8" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
@@ -2315,42 +2311,42 @@
     </row>
     <row r="4" spans="1:2" ht="84" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>88</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>90</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>92</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="140" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>94</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="126" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>96</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -2379,226 +2375,226 @@
   <sheetData>
     <row r="1" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>125</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>129</v>
+      </c>
+      <c r="B11" t="s">
         <v>130</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
+        <v>109</v>
+      </c>
+      <c r="D11" t="s">
         <v>131</v>
-      </c>
-      <c r="C11" t="s">
-        <v>110</v>
-      </c>
-      <c r="D11" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>132</v>
+      </c>
+      <c r="B12" t="s">
         <v>133</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
+        <v>109</v>
+      </c>
+      <c r="D12" t="s">
         <v>134</v>
-      </c>
-      <c r="C12" t="s">
-        <v>110</v>
-      </c>
-      <c r="D12" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
+        <v>135</v>
+      </c>
+      <c r="B13" t="s">
         <v>136</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
+        <v>109</v>
+      </c>
+      <c r="D13" t="s">
         <v>137</v>
-      </c>
-      <c r="C13" t="s">
-        <v>110</v>
-      </c>
-      <c r="D13" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>138</v>
+      </c>
+      <c r="B14" t="s">
         <v>139</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
+        <v>109</v>
+      </c>
+      <c r="D14" t="s">
         <v>140</v>
-      </c>
-      <c r="C14" t="s">
-        <v>110</v>
-      </c>
-      <c r="D14" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>141</v>
+      </c>
+      <c r="B15" t="s">
         <v>142</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
+        <v>109</v>
+      </c>
+      <c r="D15" t="s">
         <v>143</v>
-      </c>
-      <c r="C15" t="s">
-        <v>110</v>
-      </c>
-      <c r="D15" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>144</v>
+      </c>
+      <c r="B16" t="s">
         <v>145</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
+        <v>109</v>
+      </c>
+      <c r="D16" t="s">
         <v>146</v>
-      </c>
-      <c r="C16" t="s">
-        <v>110</v>
-      </c>
-      <c r="D16" t="s">
-        <v>147</v>
       </c>
     </row>
   </sheetData>

--- a/docs/shows/data/shows.xlsx
+++ b/docs/shows/data/shows.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings_website/rock/docs/shows/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6CD7570-48AD-B142-9CC7-9B5DF152F9B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FAA71BF-D60E-1143-A5E0-65FF622C5D55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -117,7 +117,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="172">
   <si>
     <t>HOW TO ADD A SHOW: Fill in a new row below. Date format: YYYY-MM-DD. Start/End Time: H:MM AM/PM (e.g. 7:00 PM). Address: full street address for Maps link (e.g. 1600 Dodge Ave, Evanston, IL 60201). Cancelled: TRUE or FALSE. Cancel Reason: optional text like "venue closure" (defaults to weather). Private: TRUE for private bookings (hidden from calendar/search). Leave optional columns blank if not needed. After saving, run:  python docs/shows/update_shows.py  then commit &amp; push.</t>
   </si>
@@ -668,6 +668,9 @@
   </si>
   <si>
     <t>2027-09-11</t>
+  </si>
+  <si>
+    <t>2026-09-25</t>
   </si>
 </sst>
 </file>
@@ -2270,6 +2273,34 @@
         <v>19</v>
       </c>
     </row>
+    <row r="27" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D27" s="10">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="E27" s="10">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="F27" s="8"/>
+      <c r="G27" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="H27" s="8"/>
+      <c r="I27" s="14"/>
+      <c r="Q27" s="17"/>
+      <c r="R27" s="17"/>
+      <c r="S27" s="18"/>
+      <c r="T27" s="19"/>
+      <c r="U27" s="17"/>
+    </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="L31" s="11" t="s">
         <v>158</v>

--- a/docs/shows/data/shows.xlsx
+++ b/docs/shows/data/shows.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings_website/rock/docs/shows/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FAA71BF-D60E-1143-A5E0-65FF622C5D55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87DF19C0-5088-AF48-A9F7-69A285B0A025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Shows" sheetId="1" r:id="rId1"/>
@@ -117,7 +117,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="177">
   <si>
     <t>HOW TO ADD A SHOW: Fill in a new row below. Date format: YYYY-MM-DD. Start/End Time: H:MM AM/PM (e.g. 7:00 PM). Address: full street address for Maps link (e.g. 1600 Dodge Ave, Evanston, IL 60201). Cancelled: TRUE or FALSE. Cancel Reason: optional text like "venue closure" (defaults to weather). Private: TRUE for private bookings (hidden from calendar/search). Leave optional columns blank if not needed. After saving, run:  python docs/shows/update_shows.py  then commit &amp; push.</t>
   </si>
@@ -671,6 +671,21 @@
   </si>
   <si>
     <t>2026-09-25</t>
+  </si>
+  <si>
+    <t>Willmette Theater</t>
+  </si>
+  <si>
+    <t>https://www.wilmettetheatre.com/</t>
+  </si>
+  <si>
+    <t>1122 Central Ave., Wilmette, IL 60091</t>
+  </si>
+  <si>
+    <t>Live Local Music</t>
+  </si>
+  <si>
+    <t>https://livelocal.music/</t>
   </si>
 </sst>
 </file>
@@ -862,7 +877,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -931,6 +946,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="18" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2301,6 +2322,32 @@
       <c r="T27" s="19"/>
       <c r="U27" s="17"/>
     </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A28" s="25">
+        <v>46330</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="D28" s="10">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="E28" s="26">
+        <v>0.875</v>
+      </c>
+      <c r="G28" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="H28" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="J28" s="11" t="s">
+        <v>176</v>
+      </c>
+    </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="L31" s="11" t="s">
         <v>158</v>

--- a/docs/shows/data/shows.xlsx
+++ b/docs/shows/data/shows.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings_website/rock/docs/shows/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87DF19C0-5088-AF48-A9F7-69A285B0A025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A0A8E7D-6439-6D44-B7E1-B2B955CCE600}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Shows" sheetId="1" r:id="rId1"/>
@@ -117,7 +117,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="178">
   <si>
     <t>HOW TO ADD A SHOW: Fill in a new row below. Date format: YYYY-MM-DD. Start/End Time: H:MM AM/PM (e.g. 7:00 PM). Address: full street address for Maps link (e.g. 1600 Dodge Ave, Evanston, IL 60201). Cancelled: TRUE or FALSE. Cancel Reason: optional text like "venue closure" (defaults to weather). Private: TRUE for private bookings (hidden from calendar/search). Leave optional columns blank if not needed. After saving, run:  python docs/shows/update_shows.py  then commit &amp; push.</t>
   </si>
@@ -686,6 +686,9 @@
   </si>
   <si>
     <t>https://livelocal.music/</t>
+  </si>
+  <si>
+    <t>2026-11-04</t>
   </si>
 </sst>
 </file>
@@ -877,7 +880,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -934,6 +937,9 @@
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="18" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -947,10 +953,10 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="18" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1280,7 +1286,7 @@
   <dimension ref="A1:U31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18" style="11" customWidth="1"/>
+    <col min="1" max="1" width="18" style="27" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" style="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="104.5" style="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="35.6640625" style="11" bestFit="1" customWidth="1"/>
@@ -1300,20 +1306,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
     </row>
     <row r="2" spans="1:21" ht="54" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="26" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="12" t="s">
@@ -2323,8 +2329,8 @@
       <c r="U27" s="17"/>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A28" s="25">
-        <v>46330</v>
+      <c r="A28" s="27" t="s">
+        <v>177</v>
       </c>
       <c r="B28" s="11" t="s">
         <v>172</v>
@@ -2335,7 +2341,7 @@
       <c r="D28" s="10">
         <v>0.79166666666666663</v>
       </c>
-      <c r="E28" s="26">
+      <c r="E28" s="20">
         <v>0.875</v>
       </c>
       <c r="G28" s="11" t="s">
@@ -2372,16 +2378,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="23"/>
+      <c r="B1" s="24"/>
     </row>
     <row r="2" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="B2" s="23"/>
+      <c r="B2" s="24"/>
     </row>
     <row r="3" spans="1:2" ht="8" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>

--- a/docs/shows/data/shows.xlsx
+++ b/docs/shows/data/shows.xlsx
@@ -202,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -280,6 +280,12 @@
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -674,7 +680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U31"/>
+  <dimension ref="A1:X31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="18" customWidth="1" style="27" min="1" max="1"/>
@@ -693,7 +699,9 @@
     <col width="8.83203125" customWidth="1" style="24" min="15" max="15"/>
     <col width="8.83203125" customWidth="1" style="22" min="16" max="16"/>
     <col width="12.5" customWidth="1" style="22" min="17" max="21"/>
-    <col width="8.83203125" customWidth="1" style="22" min="22" max="16384"/>
+    <col width="18" customWidth="1" style="22" min="22" max="16384"/>
+    <col width="18" customWidth="1" style="24" min="23" max="23"/>
+    <col width="22" customWidth="1" style="24" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="24">
@@ -828,6 +836,24 @@
 (mph)</t>
         </is>
       </c>
+      <c r="V2" s="28" t="inlineStr">
+        <is>
+          <t>Ticket Price
+(optional: Free, 0, or 25)</t>
+        </is>
+      </c>
+      <c r="W2" s="28" t="inlineStr">
+        <is>
+          <t>Ticket URL
+(optional)</t>
+        </is>
+      </c>
+      <c r="X2" s="28" t="inlineStr">
+        <is>
+          <t>Ticket Note
+(optional, e.g. includes a free drink)</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="20" customHeight="1" s="24">
       <c r="A3" s="13" t="inlineStr">
@@ -873,6 +899,11 @@
       </c>
       <c r="U3" s="17" t="n">
         <v>9.6</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" s="24">
@@ -966,6 +997,11 @@
       </c>
       <c r="U5" s="17" t="n">
         <v>17.2</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" s="24">
@@ -1094,6 +1130,11 @@
       <c r="U8" s="17" t="n">
         <v>10.4</v>
       </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="20" customHeight="1" s="24">
       <c r="A9" s="13" t="inlineStr">
@@ -1139,6 +1180,11 @@
       </c>
       <c r="U9" s="17" t="n">
         <v>14.6</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" s="24">
@@ -1201,6 +1247,11 @@
       <c r="U10" s="17" t="n">
         <v>9.1</v>
       </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="24">
       <c r="A11" s="13" t="inlineStr">
@@ -1298,6 +1349,11 @@
       </c>
       <c r="U12" s="17" t="n">
         <v>7.7</v>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" s="24">
@@ -1389,6 +1445,11 @@
       <c r="U14" s="17" t="n">
         <v>12.6</v>
       </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="20" customHeight="1" s="24">
       <c r="A15" s="13" t="inlineStr">
@@ -1766,6 +1827,11 @@
       </c>
       <c r="U21" s="17" t="n">
         <v>8.4</v>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1" s="24">
@@ -1965,6 +2031,11 @@
         </is>
       </c>
       <c r="Q25" t="n"/>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="20" customHeight="1" s="24">
       <c r="A26" s="13" t="inlineStr">
@@ -1999,6 +2070,11 @@
         </is>
       </c>
       <c r="Q26" t="n"/>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="20" customHeight="1" s="24">
       <c r="A27" s="13" t="inlineStr">
@@ -2035,6 +2111,11 @@
       <c r="S27" s="18" t="n"/>
       <c r="T27" s="19" t="n"/>
       <c r="U27" s="17" t="n"/>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="27" t="inlineStr">
@@ -2044,7 +2125,7 @@
       </c>
       <c r="B28" s="22" t="inlineStr">
         <is>
-          <t>Willmette Theater</t>
+          <t>Wilmette Theatre</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -2074,7 +2155,19 @@
           <t>https://livelocal.music/</t>
         </is>
       </c>
-    </row>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>includes a free drink</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30"/>
     <row r="31">
       <c r="L31" s="22" t="inlineStr">
         <is>
@@ -2220,7 +2313,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" style="24" min="1" max="1"/>
@@ -2581,6 +2674,72 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="29" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="B17" s="29" t="inlineStr">
+        <is>
+          <t>Ticket Price</t>
+        </is>
+      </c>
+      <c r="C17" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D17" s="29" t="inlineStr">
+        <is>
+          <t>Blank = unknown (no price published to Google). "Free" or 0 = free event. Otherwise the number, e.g. 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="29" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B18" s="29" t="inlineStr">
+        <is>
+          <t>Ticket URL</t>
+        </is>
+      </c>
+      <c r="C18" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D18" s="29" t="inlineStr">
+        <is>
+          <t>Direct ticket link. Falls back to Venue URL when blank.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B19" s="29" t="inlineStr">
+        <is>
+          <t>Ticket Note</t>
+        </is>
+      </c>
+      <c r="C19" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D19" s="29" t="inlineStr">
+        <is>
+          <t>Short qualifier shown in parentheses after the price, e.g. "includes a free drink". Only appears when a price is set.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/shows/data/shows.xlsx
+++ b/docs/shows/data/shows.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings_website/rock/docs/shows/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DD70DCD-D500-344A-9515-A9F714910BBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19F7A87B-C22C-4B49-8FFF-5D4D7C07520D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -92,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="194">
   <si>
     <t>HOW TO ADD A SHOW: Fill in a new row below. Date format: YYYY-MM-DD. Start/End Time: H:MM AM/PM (e.g. 7:00 PM). Address: full street address for Maps link (e.g. 1600 Dodge Ave, Evanston, IL 60201). Cancelled: TRUE or FALSE. Cancel Reason: optional text like "venue closure" (defaults to weather). Private: TRUE for private bookings (hidden from calendar/search). Leave optional columns blank if not needed. After saving, run:  python docs/shows/update_shows.py  then commit &amp; push.</t>
   </si>
@@ -712,6 +712,9 @@
   </si>
   <si>
     <t>2028-09-09</t>
+  </si>
+  <si>
+    <t>2026-10-03</t>
   </si>
 </sst>
 </file>
@@ -2397,6 +2400,37 @@
         <v>119</v>
       </c>
     </row>
+    <row r="29" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D29" s="10">
+        <v>0.75</v>
+      </c>
+      <c r="E29" s="10">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="F29" s="8"/>
+      <c r="G29" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="H29" s="8"/>
+      <c r="I29" s="14"/>
+      <c r="Q29" s="17"/>
+      <c r="R29" s="17"/>
+      <c r="S29" s="18"/>
+      <c r="T29" s="19"/>
+      <c r="U29" s="17"/>
+      <c r="V29" t="s">
+        <v>29</v>
+      </c>
+    </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="L31" s="11" t="s">
         <v>120</v>

--- a/docs/shows/data/shows.xlsx
+++ b/docs/shows/data/shows.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings_website/rock/docs/shows/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19F7A87B-C22C-4B49-8FFF-5D4D7C07520D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0925DEF-D199-0F46-9632-1713062B67D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -92,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="193">
   <si>
     <t>HOW TO ADD A SHOW: Fill in a new row below. Date format: YYYY-MM-DD. Start/End Time: H:MM AM/PM (e.g. 7:00 PM). Address: full street address for Maps link (e.g. 1600 Dodge Ave, Evanston, IL 60201). Cancelled: TRUE or FALSE. Cancel Reason: optional text like "venue closure" (defaults to weather). Private: TRUE for private bookings (hidden from calendar/search). Leave optional columns blank if not needed. After saving, run:  python docs/shows/update_shows.py  then commit &amp; push.</t>
   </si>
@@ -712,9 +712,6 @@
   </si>
   <si>
     <t>2028-09-09</t>
-  </si>
-  <si>
-    <t>2026-10-03</t>
   </si>
 </sst>
 </file>
@@ -1280,7 +1277,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X31"/>
+  <dimension ref="A1:X30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="18" defaultRowHeight="17" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" style="22" customWidth="1"/>
@@ -2400,39 +2397,8 @@
         <v>119</v>
       </c>
     </row>
-    <row r="29" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D29" s="10">
-        <v>0.75</v>
-      </c>
-      <c r="E29" s="10">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="F29" s="8"/>
-      <c r="G29" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="H29" s="8"/>
-      <c r="I29" s="14"/>
-      <c r="Q29" s="17"/>
-      <c r="R29" s="17"/>
-      <c r="S29" s="18"/>
-      <c r="T29" s="19"/>
-      <c r="U29" s="17"/>
-      <c r="V29" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="L31" s="11" t="s">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="L30" s="11" t="s">
         <v>120</v>
       </c>
     </row>
